--- a/DataframeCorrelacao.xlsx
+++ b/DataframeCorrelacao.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuri\Desktop\Overleaf - Métodos Quantitativos II\Aula 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuri\Desktop\Overleaf - Métodos Quantitativos II\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -45,22 +45,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -86,12 +74,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,15 +358,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="8.88671875" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
@@ -399,8 +380,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>122484</v>
+      <c r="B2">
+        <v>118000</v>
       </c>
       <c r="C2">
         <v>13.2</v>
@@ -416,8 +397,8 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>119309</v>
+      <c r="B3">
+        <v>120500</v>
       </c>
       <c r="C3">
         <v>13</v>
@@ -433,8 +414,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>123238</v>
+      <c r="B4">
+        <v>117200</v>
       </c>
       <c r="C4">
         <v>13.5</v>
@@ -450,8 +431,8 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>127615</v>
+      <c r="B5">
+        <v>122000</v>
       </c>
       <c r="C5">
         <v>12.8</v>
@@ -467,8 +448,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>118829</v>
+      <c r="B6">
+        <v>115800</v>
       </c>
       <c r="C6">
         <v>13.7</v>
@@ -484,8 +465,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>118829</v>
+      <c r="B7">
+        <v>123500</v>
       </c>
       <c r="C7">
         <v>12.5</v>
@@ -501,8 +482,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>127896</v>
+      <c r="B8">
+        <v>119300</v>
       </c>
       <c r="C8">
         <v>13.1</v>
@@ -518,8 +499,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>123837</v>
+      <c r="B9">
+        <v>121700</v>
       </c>
       <c r="C9">
         <v>12.9</v>
@@ -535,8 +516,8 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>117653</v>
+      <c r="B10">
+        <v>116400</v>
       </c>
       <c r="C10">
         <v>13.6</v>
@@ -552,8 +533,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>122713</v>
+      <c r="B11">
+        <v>124200</v>
       </c>
       <c r="C11">
         <v>12.4</v>
@@ -569,8 +550,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>117683</v>
+      <c r="B12">
+        <v>125000</v>
       </c>
       <c r="C12">
         <v>12.3</v>
@@ -586,8 +567,8 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>117671</v>
+      <c r="B13">
+        <v>114800</v>
       </c>
       <c r="C13">
         <v>13.9</v>
@@ -603,8 +584,8 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>121210</v>
+      <c r="B14">
+        <v>126500</v>
       </c>
       <c r="C14">
         <v>12.1</v>
@@ -620,8 +601,8 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>110434</v>
+      <c r="B15">
+        <v>113500</v>
       </c>
       <c r="C15">
         <v>14.1</v>
@@ -637,8 +618,8 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>111375</v>
+      <c r="B16">
+        <v>127200</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -654,8 +635,8 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
-        <v>117189</v>
+      <c r="B17">
+        <v>112000</v>
       </c>
       <c r="C17">
         <v>14.3</v>
@@ -671,8 +652,8 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
-        <v>114936</v>
+      <c r="B18">
+        <v>128800</v>
       </c>
       <c r="C18">
         <v>11.8</v>
@@ -688,8 +669,8 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>121571</v>
+      <c r="B19">
+        <v>111200</v>
       </c>
       <c r="C19">
         <v>14.5</v>
@@ -705,8 +686,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>115460</v>
+      <c r="B20">
+        <v>130000</v>
       </c>
       <c r="C20">
         <v>11.6</v>
@@ -722,8 +703,8 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
-        <v>112938</v>
+      <c r="B21">
+        <v>110500</v>
       </c>
       <c r="C21">
         <v>14.7</v>
@@ -739,8 +720,8 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
-        <v>127328</v>
+      <c r="B22">
+        <v>131500</v>
       </c>
       <c r="C22">
         <v>11.5</v>
@@ -756,8 +737,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
-        <v>118871</v>
+      <c r="B23">
+        <v>109800</v>
       </c>
       <c r="C23">
         <v>14.9</v>
@@ -773,8 +754,8 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
-        <v>120338</v>
+      <c r="B24">
+        <v>132800</v>
       </c>
       <c r="C24">
         <v>11.3</v>
@@ -790,8 +771,8 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
-        <v>112876</v>
+      <c r="B25">
+        <v>109000</v>
       </c>
       <c r="C25">
         <v>15</v>
@@ -807,8 +788,8 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
-        <v>117278</v>
+      <c r="B26">
+        <v>134200</v>
       </c>
       <c r="C26">
         <v>11.2</v>
@@ -824,8 +805,8 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>120555</v>
+      <c r="B27">
+        <v>108500</v>
       </c>
       <c r="C27">
         <v>15.2</v>
@@ -841,8 +822,8 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>114245</v>
+      <c r="B28">
+        <v>135500</v>
       </c>
       <c r="C28">
         <v>11</v>
@@ -858,8 +839,8 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
-        <v>121878</v>
+      <c r="B29">
+        <v>108000</v>
       </c>
       <c r="C29">
         <v>15.3</v>
@@ -875,8 +856,8 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
-        <v>116997</v>
+      <c r="B30">
+        <v>137000</v>
       </c>
       <c r="C30">
         <v>10.8</v>
@@ -892,8 +873,8 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
-        <v>118542</v>
+      <c r="B31">
+        <v>107500</v>
       </c>
       <c r="C31">
         <v>15.5</v>
@@ -909,8 +890,8 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
-        <v>116991</v>
+      <c r="B32">
+        <v>138500</v>
       </c>
       <c r="C32">
         <v>10.6</v>
@@ -926,8 +907,8 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
-        <v>129261</v>
+      <c r="B33">
+        <v>107000</v>
       </c>
       <c r="C33">
         <v>15.7</v>
@@ -943,8 +924,8 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
-        <v>119933</v>
+      <c r="B34">
+        <v>140000</v>
       </c>
       <c r="C34">
         <v>10.5</v>
@@ -960,8 +941,8 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
-        <v>114711</v>
+      <c r="B35">
+        <v>106500</v>
       </c>
       <c r="C35">
         <v>15.8</v>
@@ -977,8 +958,8 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
-        <v>124113</v>
+      <c r="B36">
+        <v>141500</v>
       </c>
       <c r="C36">
         <v>10.3</v>
@@ -994,8 +975,8 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
-        <v>113896</v>
+      <c r="B37">
+        <v>106000</v>
       </c>
       <c r="C37">
         <v>16</v>
@@ -1011,8 +992,8 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
-        <v>121044</v>
+      <c r="B38">
+        <v>143000</v>
       </c>
       <c r="C38">
         <v>10.1</v>
@@ -1028,8 +1009,8 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
-        <v>110202</v>
+      <c r="B39">
+        <v>105500</v>
       </c>
       <c r="C39">
         <v>16.2</v>
@@ -1045,8 +1026,8 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
-        <v>113359</v>
+      <c r="B40">
+        <v>144500</v>
       </c>
       <c r="C40">
         <v>10</v>
@@ -1062,8 +1043,8 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
-        <v>120984</v>
+      <c r="B41">
+        <v>105000</v>
       </c>
       <c r="C41">
         <v>16.399999999999999</v>
@@ -1079,8 +1060,8 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="2">
-        <v>123692</v>
+      <c r="B42">
+        <v>146000</v>
       </c>
       <c r="C42">
         <v>9.8000000000000007</v>
@@ -1096,8 +1077,8 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
-        <v>120857</v>
+      <c r="B43">
+        <v>104500</v>
       </c>
       <c r="C43">
         <v>16.600000000000001</v>
@@ -1113,8 +1094,8 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="2">
-        <v>119422</v>
+      <c r="B44">
+        <v>147500</v>
       </c>
       <c r="C44">
         <v>9.6</v>
@@ -1130,8 +1111,8 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
-        <v>118494</v>
+      <c r="B45">
+        <v>104000</v>
       </c>
       <c r="C45">
         <v>16.8</v>
@@ -1147,8 +1128,8 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="2">
-        <v>112607</v>
+      <c r="B46">
+        <v>149000</v>
       </c>
       <c r="C46">
         <v>9.5</v>
@@ -1164,8 +1145,8 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
-        <v>116401</v>
+      <c r="B47">
+        <v>103500</v>
       </c>
       <c r="C47">
         <v>17</v>
@@ -1181,8 +1162,8 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
-        <v>117697</v>
+      <c r="B48">
+        <v>150500</v>
       </c>
       <c r="C48">
         <v>9.3000000000000007</v>
@@ -1198,8 +1179,8 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
-        <v>125286</v>
+      <c r="B49">
+        <v>103000</v>
       </c>
       <c r="C49">
         <v>17.2</v>
@@ -1215,8 +1196,8 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="2">
-        <v>121718</v>
+      <c r="B50">
+        <v>152000</v>
       </c>
       <c r="C50">
         <v>9.1</v>
@@ -1232,8 +1213,8 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="2">
-        <v>111185</v>
+      <c r="B51">
+        <v>102500</v>
       </c>
       <c r="C51">
         <v>17.5</v>
@@ -1247,6 +1228,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>